--- a/Luban/Data/__tables__.xlsx
+++ b/Luban/Data/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -740,6 +740,50 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>TbCombatNum</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>CombatNum</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>#combatnum.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>玩法数值表（单行：手感参数；消费点 CombatConfig）</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
